--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MISSISSIPPI_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/MISSISSIPPI_2013.xlsx
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C78">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C121">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C328">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C366">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C368">
